--- a/sim-output/dallas-2026_results.xlsx
+++ b/sim-output/dallas-2026_results.xlsx
@@ -112,40 +112,40 @@
     <t>+669</t>
   </si>
   <si>
-    <t>+842</t>
-  </si>
-  <si>
-    <t>+1280</t>
-  </si>
-  <si>
-    <t>+1657</t>
-  </si>
-  <si>
-    <t>+1985</t>
-  </si>
-  <si>
-    <t>+2029</t>
-  </si>
-  <si>
-    <t>+2282</t>
-  </si>
-  <si>
-    <t>+2404</t>
-  </si>
-  <si>
-    <t>+3269</t>
-  </si>
-  <si>
-    <t>+9660</t>
-  </si>
-  <si>
-    <t>+11364</t>
-  </si>
-  <si>
-    <t>+15988</t>
-  </si>
-  <si>
-    <t>+25287</t>
+    <t>+841</t>
+  </si>
+  <si>
+    <t>+1275</t>
+  </si>
+  <si>
+    <t>+1663</t>
+  </si>
+  <si>
+    <t>+1999</t>
+  </si>
+  <si>
+    <t>+2031</t>
+  </si>
+  <si>
+    <t>+2298</t>
+  </si>
+  <si>
+    <t>+2377</t>
+  </si>
+  <si>
+    <t>+3303</t>
+  </si>
+  <si>
+    <t>+9747</t>
+  </si>
+  <si>
+    <t>+11027</t>
+  </si>
+  <si>
+    <t>+16079</t>
+  </si>
+  <si>
+    <t>+24591</t>
   </si>
   <si>
     <t>N/A</t>
@@ -549,16 +549,16 @@
         <v>25</v>
       </c>
       <c r="E2">
-        <v>83.77</v>
+        <v>83.84</v>
       </c>
       <c r="F2">
-        <v>55.66</v>
+        <v>55.75</v>
       </c>
       <c r="G2">
-        <v>38.14</v>
+        <v>38.18</v>
       </c>
       <c r="H2">
-        <v>25.56</v>
+        <v>25.58</v>
       </c>
       <c r="I2" t="s">
         <v>29</v>
@@ -575,16 +575,16 @@
         <v>26</v>
       </c>
       <c r="E3">
-        <v>61.85</v>
+        <v>61.86</v>
       </c>
       <c r="F3">
-        <v>37.3</v>
+        <v>37.33</v>
       </c>
       <c r="G3">
-        <v>26.33</v>
+        <v>26.35</v>
       </c>
       <c r="H3">
-        <v>14.31</v>
+        <v>14.3</v>
       </c>
       <c r="I3" t="s">
         <v>30</v>
@@ -604,13 +604,13 @@
         <v>100</v>
       </c>
       <c r="F4">
-        <v>59.79</v>
+        <v>59.86</v>
       </c>
       <c r="G4">
-        <v>25.06</v>
+        <v>25.1</v>
       </c>
       <c r="H4">
-        <v>13</v>
+        <v>13.01</v>
       </c>
       <c r="I4" t="s">
         <v>31</v>
@@ -627,16 +627,16 @@
         <v>25</v>
       </c>
       <c r="E5">
-        <v>71.90000000000001</v>
+        <v>71.87</v>
       </c>
       <c r="F5">
-        <v>32.36</v>
+        <v>32.32</v>
       </c>
       <c r="G5">
-        <v>18.83</v>
+        <v>18.78</v>
       </c>
       <c r="H5">
-        <v>10.62</v>
+        <v>10.63</v>
       </c>
       <c r="I5" t="s">
         <v>32</v>
@@ -653,16 +653,16 @@
         <v>26</v>
       </c>
       <c r="E6">
-        <v>54.19</v>
+        <v>54.29</v>
       </c>
       <c r="F6">
-        <v>25</v>
+        <v>25.04</v>
       </c>
       <c r="G6">
-        <v>15.79</v>
+        <v>15.8</v>
       </c>
       <c r="H6">
-        <v>7.25</v>
+        <v>7.27</v>
       </c>
       <c r="I6" t="s">
         <v>33</v>
@@ -679,16 +679,16 @@
         <v>27</v>
       </c>
       <c r="E7">
-        <v>68.37</v>
+        <v>68.31999999999999</v>
       </c>
       <c r="F7">
-        <v>31.29</v>
+        <v>31.25</v>
       </c>
       <c r="G7">
-        <v>11.94</v>
+        <v>11.88</v>
       </c>
       <c r="H7">
-        <v>5.69</v>
+        <v>5.67</v>
       </c>
       <c r="I7" t="s">
         <v>34</v>
@@ -705,16 +705,16 @@
         <v>26</v>
       </c>
       <c r="E8">
-        <v>45.81</v>
+        <v>45.71</v>
       </c>
       <c r="F8">
-        <v>19.26</v>
+        <v>19.18</v>
       </c>
       <c r="G8">
-        <v>11.38</v>
+        <v>11.34</v>
       </c>
       <c r="H8">
-        <v>4.8</v>
+        <v>4.76</v>
       </c>
       <c r="I8" t="s">
         <v>35</v>
@@ -731,16 +731,16 @@
         <v>26</v>
       </c>
       <c r="E9">
-        <v>38.15</v>
+        <v>38.14</v>
       </c>
       <c r="F9">
-        <v>18.44</v>
+        <v>18.45</v>
       </c>
       <c r="G9">
-        <v>11.03</v>
+        <v>11.01</v>
       </c>
       <c r="H9">
-        <v>4.7</v>
+        <v>4.69</v>
       </c>
       <c r="I9" t="s">
         <v>36</v>
@@ -757,16 +757,16 @@
         <v>28</v>
       </c>
       <c r="E10">
-        <v>61.94</v>
+        <v>61.85</v>
       </c>
       <c r="F10">
-        <v>31.37</v>
+        <v>31.3</v>
       </c>
       <c r="G10">
-        <v>11.73</v>
+        <v>11.7</v>
       </c>
       <c r="H10">
-        <v>4.2</v>
+        <v>4.17</v>
       </c>
       <c r="I10" t="s">
         <v>37</v>
@@ -783,16 +783,16 @@
         <v>28</v>
       </c>
       <c r="E11">
-        <v>52.76</v>
+        <v>52.91</v>
       </c>
       <c r="F11">
-        <v>29.08</v>
+        <v>29.21</v>
       </c>
       <c r="G11">
-        <v>11.05</v>
+        <v>11.09</v>
       </c>
       <c r="H11">
-        <v>3.99</v>
+        <v>4.04</v>
       </c>
       <c r="I11" t="s">
         <v>38</v>
@@ -809,16 +809,16 @@
         <v>28</v>
       </c>
       <c r="E12">
-        <v>47.24</v>
+        <v>47.09</v>
       </c>
       <c r="F12">
-        <v>24.79</v>
+        <v>24.7</v>
       </c>
       <c r="G12">
-        <v>8.75</v>
+        <v>8.76</v>
       </c>
       <c r="H12">
-        <v>2.97</v>
+        <v>2.94</v>
       </c>
       <c r="I12" t="s">
         <v>39</v>
@@ -835,13 +835,13 @@
         <v>28</v>
       </c>
       <c r="E13">
-        <v>38.06</v>
+        <v>38.15</v>
       </c>
       <c r="F13">
-        <v>14.76</v>
+        <v>14.79</v>
       </c>
       <c r="G13">
-        <v>3.94</v>
+        <v>3.97</v>
       </c>
       <c r="H13">
         <v>1.02</v>
@@ -861,16 +861,16 @@
         <v>25</v>
       </c>
       <c r="E14">
-        <v>28.1</v>
+        <v>28.13</v>
       </c>
       <c r="F14">
-        <v>7.25</v>
+        <v>7.28</v>
       </c>
       <c r="G14">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="H14">
-        <v>0.87</v>
+        <v>0.9</v>
       </c>
       <c r="I14" t="s">
         <v>41</v>
@@ -887,13 +887,13 @@
         <v>27</v>
       </c>
       <c r="E15">
-        <v>31.63</v>
+        <v>31.68</v>
       </c>
       <c r="F15">
-        <v>8.92</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="G15">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H15">
         <v>0.62</v>
@@ -913,16 +913,16 @@
         <v>25</v>
       </c>
       <c r="E16">
-        <v>16.23</v>
+        <v>16.16</v>
       </c>
       <c r="F16">
-        <v>4.73</v>
+        <v>4.65</v>
       </c>
       <c r="G16">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="H16">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="I16" t="s">
         <v>43</v>

--- a/sim-output/dallas-2026_results.xlsx
+++ b/sim-output/dallas-2026_results.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="42">
   <si>
     <t>Player</t>
   </si>
@@ -58,36 +58,36 @@
     <t>Sebastian Korda</t>
   </si>
   <si>
+    <t>Eliot Spizzirri</t>
+  </si>
+  <si>
     <t>Denis Shapovalov</t>
   </si>
   <si>
+    <t>Marin Cilic</t>
+  </si>
+  <si>
+    <t>Ethan Quinn</t>
+  </si>
+  <si>
+    <t>Miomir Kecmanovic</t>
+  </si>
+  <si>
+    <t>Aleksandar Kovacevic</t>
+  </si>
+  <si>
+    <t>Adrian Mannarino</t>
+  </si>
+  <si>
+    <t>Brandon Nakashima</t>
+  </si>
+  <si>
     <t>Frances Tiafoe</t>
   </si>
   <si>
-    <t>Brandon Nakashima</t>
-  </si>
-  <si>
-    <t>Eliot Spizzirri</t>
-  </si>
-  <si>
-    <t>Marin Cilic</t>
-  </si>
-  <si>
-    <t>Ethan Quinn</t>
-  </si>
-  <si>
     <t>Qualifier1</t>
   </si>
   <si>
-    <t>Miomir Kecmanovic</t>
-  </si>
-  <si>
-    <t>Aleksandar Kovacevic</t>
-  </si>
-  <si>
-    <t>Adrian Mannarino</t>
-  </si>
-  <si>
     <t>Alex Michelsen</t>
   </si>
   <si>
@@ -103,49 +103,40 @@
     <t>Q2</t>
   </si>
   <si>
-    <t>+291</t>
-  </si>
-  <si>
-    <t>+599</t>
-  </si>
-  <si>
-    <t>+669</t>
-  </si>
-  <si>
-    <t>+841</t>
-  </si>
-  <si>
-    <t>+1275</t>
-  </si>
-  <si>
-    <t>+1663</t>
-  </si>
-  <si>
-    <t>+1999</t>
-  </si>
-  <si>
-    <t>+2031</t>
-  </si>
-  <si>
-    <t>+2298</t>
-  </si>
-  <si>
-    <t>+2377</t>
-  </si>
-  <si>
-    <t>+3303</t>
-  </si>
-  <si>
-    <t>+9747</t>
-  </si>
-  <si>
-    <t>+11027</t>
-  </si>
-  <si>
-    <t>+16079</t>
-  </si>
-  <si>
-    <t>+24591</t>
+    <t>+314</t>
+  </si>
+  <si>
+    <t>+327</t>
+  </si>
+  <si>
+    <t>+746</t>
+  </si>
+  <si>
+    <t>+809</t>
+  </si>
+  <si>
+    <t>+886</t>
+  </si>
+  <si>
+    <t>+1404</t>
+  </si>
+  <si>
+    <t>+1724</t>
+  </si>
+  <si>
+    <t>+2337</t>
+  </si>
+  <si>
+    <t>+6314</t>
+  </si>
+  <si>
+    <t>+15581</t>
+  </si>
+  <si>
+    <t>+20316</t>
+  </si>
+  <si>
+    <t>+20375</t>
   </si>
   <si>
     <t>N/A</t>
@@ -549,16 +540,16 @@
         <v>25</v>
       </c>
       <c r="E2">
-        <v>83.84</v>
+        <v>82.62</v>
       </c>
       <c r="F2">
-        <v>55.75</v>
+        <v>54.46</v>
       </c>
       <c r="G2">
-        <v>38.18</v>
+        <v>37.56</v>
       </c>
       <c r="H2">
-        <v>25.58</v>
+        <v>24.18</v>
       </c>
       <c r="I2" t="s">
         <v>29</v>
@@ -575,16 +566,16 @@
         <v>26</v>
       </c>
       <c r="E3">
-        <v>61.86</v>
+        <v>100</v>
       </c>
       <c r="F3">
-        <v>37.33</v>
+        <v>61.16</v>
       </c>
       <c r="G3">
-        <v>26.35</v>
+        <v>42.57</v>
       </c>
       <c r="H3">
-        <v>14.3</v>
+        <v>23.44</v>
       </c>
       <c r="I3" t="s">
         <v>30</v>
@@ -604,13 +595,13 @@
         <v>100</v>
       </c>
       <c r="F4">
-        <v>59.86</v>
+        <v>59.37</v>
       </c>
       <c r="G4">
-        <v>25.1</v>
+        <v>24.44</v>
       </c>
       <c r="H4">
-        <v>13.01</v>
+        <v>11.82</v>
       </c>
       <c r="I4" t="s">
         <v>31</v>
@@ -627,16 +618,16 @@
         <v>25</v>
       </c>
       <c r="E5">
-        <v>71.87</v>
+        <v>74.19</v>
       </c>
       <c r="F5">
-        <v>32.32</v>
+        <v>33.98</v>
       </c>
       <c r="G5">
-        <v>18.78</v>
+        <v>20.14</v>
       </c>
       <c r="H5">
-        <v>10.63</v>
+        <v>11</v>
       </c>
       <c r="I5" t="s">
         <v>32</v>
@@ -653,16 +644,16 @@
         <v>26</v>
       </c>
       <c r="E6">
-        <v>54.29</v>
+        <v>100</v>
       </c>
       <c r="F6">
-        <v>25.04</v>
+        <v>38.84</v>
       </c>
       <c r="G6">
-        <v>15.8</v>
+        <v>23.01</v>
       </c>
       <c r="H6">
-        <v>7.27</v>
+        <v>10.15</v>
       </c>
       <c r="I6" t="s">
         <v>33</v>
@@ -673,22 +664,22 @@
         <v>14</v>
       </c>
       <c r="C7">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E7">
-        <v>68.31999999999999</v>
+        <v>100</v>
       </c>
       <c r="F7">
-        <v>31.25</v>
+        <v>52.19</v>
       </c>
       <c r="G7">
-        <v>11.88</v>
+        <v>18.34</v>
       </c>
       <c r="H7">
-        <v>5.67</v>
+        <v>6.65</v>
       </c>
       <c r="I7" t="s">
         <v>34</v>
@@ -699,22 +690,22 @@
         <v>15</v>
       </c>
       <c r="C8">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E8">
-        <v>45.71</v>
+        <v>69.52</v>
       </c>
       <c r="F8">
-        <v>19.18</v>
+        <v>32.21</v>
       </c>
       <c r="G8">
-        <v>11.34</v>
+        <v>12.19</v>
       </c>
       <c r="H8">
-        <v>4.76</v>
+        <v>5.48</v>
       </c>
       <c r="I8" t="s">
         <v>35</v>
@@ -725,22 +716,22 @@
         <v>16</v>
       </c>
       <c r="C9">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D9" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E9">
-        <v>38.14</v>
+        <v>58.37</v>
       </c>
       <c r="F9">
-        <v>18.45</v>
+        <v>29.93</v>
       </c>
       <c r="G9">
-        <v>11.01</v>
+        <v>10.92</v>
       </c>
       <c r="H9">
-        <v>4.69</v>
+        <v>4.1</v>
       </c>
       <c r="I9" t="s">
         <v>36</v>
@@ -751,22 +742,22 @@
         <v>17</v>
       </c>
       <c r="C10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D10" t="s">
         <v>28</v>
       </c>
       <c r="E10">
-        <v>61.85</v>
+        <v>41.63</v>
       </c>
       <c r="F10">
-        <v>31.3</v>
+        <v>17.88</v>
       </c>
       <c r="G10">
-        <v>11.7</v>
+        <v>5.16</v>
       </c>
       <c r="H10">
-        <v>4.17</v>
+        <v>1.56</v>
       </c>
       <c r="I10" t="s">
         <v>37</v>
@@ -777,22 +768,22 @@
         <v>18</v>
       </c>
       <c r="C11">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D11" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E11">
-        <v>52.91</v>
+        <v>25.81</v>
       </c>
       <c r="F11">
-        <v>29.21</v>
+        <v>6.3</v>
       </c>
       <c r="G11">
-        <v>11.09</v>
+        <v>2.16</v>
       </c>
       <c r="H11">
-        <v>4.04</v>
+        <v>0.64</v>
       </c>
       <c r="I11" t="s">
         <v>38</v>
@@ -803,22 +794,22 @@
         <v>19</v>
       </c>
       <c r="C12">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E12">
-        <v>47.09</v>
+        <v>30.48</v>
       </c>
       <c r="F12">
-        <v>24.7</v>
+        <v>8.42</v>
       </c>
       <c r="G12">
-        <v>8.76</v>
+        <v>1.83</v>
       </c>
       <c r="H12">
-        <v>2.94</v>
+        <v>0.49</v>
       </c>
       <c r="I12" t="s">
         <v>39</v>
@@ -829,22 +820,22 @@
         <v>20</v>
       </c>
       <c r="C13">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D13" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E13">
-        <v>38.15</v>
+        <v>17.38</v>
       </c>
       <c r="F13">
-        <v>14.79</v>
+        <v>5.26</v>
       </c>
       <c r="G13">
-        <v>3.97</v>
+        <v>1.69</v>
       </c>
       <c r="H13">
-        <v>1.02</v>
+        <v>0.49</v>
       </c>
       <c r="I13" t="s">
         <v>40</v>
@@ -855,22 +846,22 @@
         <v>21</v>
       </c>
       <c r="C14">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="D14" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E14">
-        <v>28.13</v>
+        <v>0</v>
       </c>
       <c r="F14">
-        <v>7.28</v>
+        <v>0</v>
       </c>
       <c r="G14">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="H14">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="I14" t="s">
         <v>41</v>
@@ -881,25 +872,25 @@
         <v>22</v>
       </c>
       <c r="C15">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D15" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E15">
-        <v>31.68</v>
+        <v>0</v>
       </c>
       <c r="F15">
-        <v>8.880000000000001</v>
+        <v>0</v>
       </c>
       <c r="G15">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="H15">
-        <v>0.62</v>
+        <v>0</v>
       </c>
       <c r="I15" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -907,25 +898,25 @@
         <v>23</v>
       </c>
       <c r="C16">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="D16" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E16">
-        <v>16.16</v>
+        <v>0</v>
       </c>
       <c r="F16">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="G16">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="H16">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="I16" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -951,7 +942,7 @@
         <v>0</v>
       </c>
       <c r="I17" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>

--- a/sim-output/dallas-2026_results.xlsx
+++ b/sim-output/dallas-2026_results.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="43">
   <si>
     <t>Player</t>
   </si>
@@ -43,12 +43,12 @@
     <t>Title Odds</t>
   </si>
   <si>
+    <t>Taylor Fritz</t>
+  </si>
+  <si>
     <t>Ben Shelton</t>
   </si>
   <si>
-    <t>Taylor Fritz</t>
-  </si>
-  <si>
     <t>Alejandro Davidovich Fokina</t>
   </si>
   <si>
@@ -58,18 +58,21 @@
     <t>Sebastian Korda</t>
   </si>
   <si>
+    <t>Denis Shapovalov</t>
+  </si>
+  <si>
+    <t>Marin Cilic</t>
+  </si>
+  <si>
     <t>Eliot Spizzirri</t>
   </si>
   <si>
-    <t>Denis Shapovalov</t>
-  </si>
-  <si>
-    <t>Marin Cilic</t>
-  </si>
-  <si>
     <t>Ethan Quinn</t>
   </si>
   <si>
+    <t>Qualifier1</t>
+  </si>
+  <si>
     <t>Miomir Kecmanovic</t>
   </si>
   <si>
@@ -85,58 +88,58 @@
     <t>Frances Tiafoe</t>
   </si>
   <si>
-    <t>Qualifier1</t>
-  </si>
-  <si>
     <t>Alex Michelsen</t>
   </si>
   <si>
+    <t>Q1</t>
+  </si>
+  <si>
     <t>Q4</t>
   </si>
   <si>
-    <t>Q1</t>
-  </si>
-  <si>
     <t>Q3</t>
   </si>
   <si>
     <t>Q2</t>
   </si>
   <si>
-    <t>+314</t>
-  </si>
-  <si>
-    <t>+327</t>
-  </si>
-  <si>
-    <t>+746</t>
-  </si>
-  <si>
-    <t>+809</t>
-  </si>
-  <si>
-    <t>+886</t>
-  </si>
-  <si>
-    <t>+1404</t>
-  </si>
-  <si>
-    <t>+1724</t>
-  </si>
-  <si>
-    <t>+2337</t>
-  </si>
-  <si>
-    <t>+6314</t>
-  </si>
-  <si>
-    <t>+15581</t>
-  </si>
-  <si>
-    <t>+20316</t>
-  </si>
-  <si>
-    <t>+20375</t>
+    <t>-6676</t>
+  </si>
+  <si>
+    <t>+21859</t>
+  </si>
+  <si>
+    <t>+37808</t>
+  </si>
+  <si>
+    <t>+44070</t>
+  </si>
+  <si>
+    <t>+76942</t>
+  </si>
+  <si>
+    <t>+84646</t>
+  </si>
+  <si>
+    <t>+110154</t>
+  </si>
+  <si>
+    <t>+119660</t>
+  </si>
+  <si>
+    <t>+251156</t>
+  </si>
+  <si>
+    <t>+478369</t>
+  </si>
+  <si>
+    <t>+526216</t>
+  </si>
+  <si>
+    <t>+684832</t>
+  </si>
+  <si>
+    <t>+719324</t>
   </si>
   <si>
     <t>N/A</t>
@@ -534,22 +537,22 @@
         <v>9</v>
       </c>
       <c r="C2">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="D2" t="s">
         <v>25</v>
       </c>
       <c r="E2">
-        <v>82.62</v>
+        <v>100</v>
       </c>
       <c r="F2">
-        <v>54.46</v>
+        <v>99.5</v>
       </c>
       <c r="G2">
-        <v>37.56</v>
+        <v>99.01000000000001</v>
       </c>
       <c r="H2">
-        <v>24.18</v>
+        <v>98.52</v>
       </c>
       <c r="I2" t="s">
         <v>29</v>
@@ -560,22 +563,22 @@
         <v>10</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="D3" t="s">
         <v>26</v>
       </c>
       <c r="E3">
-        <v>100</v>
+        <v>82.62</v>
       </c>
       <c r="F3">
-        <v>61.16</v>
+        <v>54.47</v>
       </c>
       <c r="G3">
-        <v>42.57</v>
+        <v>37.55</v>
       </c>
       <c r="H3">
-        <v>23.44</v>
+        <v>0.46</v>
       </c>
       <c r="I3" t="s">
         <v>30</v>
@@ -595,13 +598,13 @@
         <v>100</v>
       </c>
       <c r="F4">
-        <v>59.37</v>
+        <v>59.32</v>
       </c>
       <c r="G4">
-        <v>24.44</v>
+        <v>24.41</v>
       </c>
       <c r="H4">
-        <v>11.82</v>
+        <v>0.26</v>
       </c>
       <c r="I4" t="s">
         <v>31</v>
@@ -615,19 +618,19 @@
         <v>13</v>
       </c>
       <c r="D5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E5">
-        <v>74.19</v>
+        <v>74.12</v>
       </c>
       <c r="F5">
-        <v>33.98</v>
+        <v>33.92</v>
       </c>
       <c r="G5">
-        <v>20.14</v>
+        <v>20.1</v>
       </c>
       <c r="H5">
-        <v>11</v>
+        <v>0.23</v>
       </c>
       <c r="I5" t="s">
         <v>32</v>
@@ -641,19 +644,19 @@
         <v>3</v>
       </c>
       <c r="D6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E6">
         <v>100</v>
       </c>
       <c r="F6">
-        <v>38.84</v>
+        <v>0.5</v>
       </c>
       <c r="G6">
-        <v>23.01</v>
+        <v>0.3</v>
       </c>
       <c r="H6">
-        <v>10.15</v>
+        <v>0.13</v>
       </c>
       <c r="I6" t="s">
         <v>33</v>
@@ -664,22 +667,22 @@
         <v>14</v>
       </c>
       <c r="C7">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E7">
-        <v>100</v>
+        <v>69.52</v>
       </c>
       <c r="F7">
-        <v>52.19</v>
+        <v>32.3</v>
       </c>
       <c r="G7">
-        <v>18.34</v>
+        <v>12.24</v>
       </c>
       <c r="H7">
-        <v>6.65</v>
+        <v>0.12</v>
       </c>
       <c r="I7" t="s">
         <v>34</v>
@@ -690,22 +693,22 @@
         <v>15</v>
       </c>
       <c r="C8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E8">
-        <v>69.52</v>
+        <v>58.49</v>
       </c>
       <c r="F8">
-        <v>32.21</v>
+        <v>33.06</v>
       </c>
       <c r="G8">
-        <v>12.19</v>
+        <v>0.24</v>
       </c>
       <c r="H8">
-        <v>5.48</v>
+        <v>0.09</v>
       </c>
       <c r="I8" t="s">
         <v>35</v>
@@ -716,22 +719,22 @@
         <v>16</v>
       </c>
       <c r="C9">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D9" t="s">
         <v>28</v>
       </c>
       <c r="E9">
-        <v>58.37</v>
+        <v>64.48999999999999</v>
       </c>
       <c r="F9">
-        <v>29.93</v>
+        <v>33.56</v>
       </c>
       <c r="G9">
-        <v>10.92</v>
+        <v>0.23</v>
       </c>
       <c r="H9">
-        <v>4.1</v>
+        <v>0.08</v>
       </c>
       <c r="I9" t="s">
         <v>36</v>
@@ -748,16 +751,16 @@
         <v>28</v>
       </c>
       <c r="E10">
-        <v>41.63</v>
+        <v>41.51</v>
       </c>
       <c r="F10">
-        <v>17.88</v>
+        <v>20.07</v>
       </c>
       <c r="G10">
-        <v>5.16</v>
+        <v>0.13</v>
       </c>
       <c r="H10">
-        <v>1.56</v>
+        <v>0.04</v>
       </c>
       <c r="I10" t="s">
         <v>37</v>
@@ -768,22 +771,22 @@
         <v>18</v>
       </c>
       <c r="C11">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="D11" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E11">
-        <v>25.81</v>
+        <v>35.51</v>
       </c>
       <c r="F11">
-        <v>6.3</v>
+        <v>13.31</v>
       </c>
       <c r="G11">
-        <v>2.16</v>
+        <v>0.09</v>
       </c>
       <c r="H11">
-        <v>0.64</v>
+        <v>0.02</v>
       </c>
       <c r="I11" t="s">
         <v>38</v>
@@ -794,22 +797,22 @@
         <v>19</v>
       </c>
       <c r="C12">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E12">
-        <v>30.48</v>
+        <v>25.88</v>
       </c>
       <c r="F12">
-        <v>8.42</v>
+        <v>6.34</v>
       </c>
       <c r="G12">
-        <v>1.83</v>
+        <v>2.16</v>
       </c>
       <c r="H12">
-        <v>0.49</v>
+        <v>0.02</v>
       </c>
       <c r="I12" t="s">
         <v>39</v>
@@ -820,22 +823,22 @@
         <v>20</v>
       </c>
       <c r="C13">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D13" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E13">
-        <v>17.38</v>
+        <v>30.48</v>
       </c>
       <c r="F13">
-        <v>5.26</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="G13">
-        <v>1.69</v>
+        <v>1.84</v>
       </c>
       <c r="H13">
-        <v>0.49</v>
+        <v>0.01</v>
       </c>
       <c r="I13" t="s">
         <v>40</v>
@@ -846,22 +849,22 @@
         <v>21</v>
       </c>
       <c r="C14">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D14" t="s">
         <v>26</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>17.38</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>5.27</v>
       </c>
       <c r="G14">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="I14" t="s">
         <v>41</v>
@@ -872,10 +875,10 @@
         <v>22</v>
       </c>
       <c r="C15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -890,7 +893,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -898,10 +901,10 @@
         <v>23</v>
       </c>
       <c r="C16">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D16" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -916,7 +919,7 @@
         <v>0</v>
       </c>
       <c r="I16" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -942,7 +945,7 @@
         <v>0</v>
       </c>
       <c r="I17" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>

--- a/sim-output/dallas-2026_results.xlsx
+++ b/sim-output/dallas-2026_results.xlsx
@@ -103,43 +103,43 @@
     <t>Q2</t>
   </si>
   <si>
-    <t>-6676</t>
-  </si>
-  <si>
-    <t>+21859</t>
-  </si>
-  <si>
-    <t>+37808</t>
-  </si>
-  <si>
-    <t>+44070</t>
-  </si>
-  <si>
-    <t>+76942</t>
-  </si>
-  <si>
-    <t>+84646</t>
-  </si>
-  <si>
-    <t>+110154</t>
-  </si>
-  <si>
-    <t>+119660</t>
-  </si>
-  <si>
-    <t>+251156</t>
-  </si>
-  <si>
-    <t>+478369</t>
-  </si>
-  <si>
-    <t>+526216</t>
-  </si>
-  <si>
-    <t>+684832</t>
-  </si>
-  <si>
-    <t>+719324</t>
+    <t>+292</t>
+  </si>
+  <si>
+    <t>+320</t>
+  </si>
+  <si>
+    <t>+758</t>
+  </si>
+  <si>
+    <t>+823</t>
+  </si>
+  <si>
+    <t>+890</t>
+  </si>
+  <si>
+    <t>+1744</t>
+  </si>
+  <si>
+    <t>+2165</t>
+  </si>
+  <si>
+    <t>+2282</t>
+  </si>
+  <si>
+    <t>+5730</t>
+  </si>
+  <si>
+    <t>+13898</t>
+  </si>
+  <si>
+    <t>+15608</t>
+  </si>
+  <si>
+    <t>+20430</t>
+  </si>
+  <si>
+    <t>+21006</t>
   </si>
   <si>
     <t>N/A</t>
@@ -546,13 +546,13 @@
         <v>100</v>
       </c>
       <c r="F2">
-        <v>99.5</v>
+        <v>62.55</v>
       </c>
       <c r="G2">
-        <v>99.01000000000001</v>
+        <v>45.22</v>
       </c>
       <c r="H2">
-        <v>98.52</v>
+        <v>25.53</v>
       </c>
       <c r="I2" t="s">
         <v>29</v>
@@ -569,16 +569,16 @@
         <v>26</v>
       </c>
       <c r="E3">
-        <v>82.62</v>
+        <v>82.73</v>
       </c>
       <c r="F3">
-        <v>54.47</v>
+        <v>54.45</v>
       </c>
       <c r="G3">
-        <v>37.55</v>
+        <v>37.49</v>
       </c>
       <c r="H3">
-        <v>0.46</v>
+        <v>23.81</v>
       </c>
       <c r="I3" t="s">
         <v>30</v>
@@ -598,13 +598,13 @@
         <v>100</v>
       </c>
       <c r="F4">
-        <v>59.32</v>
+        <v>59.29</v>
       </c>
       <c r="G4">
-        <v>24.41</v>
+        <v>24.47</v>
       </c>
       <c r="H4">
-        <v>0.26</v>
+        <v>11.66</v>
       </c>
       <c r="I4" t="s">
         <v>31</v>
@@ -621,16 +621,16 @@
         <v>26</v>
       </c>
       <c r="E5">
-        <v>74.12</v>
+        <v>74.13</v>
       </c>
       <c r="F5">
-        <v>33.92</v>
+        <v>33.95</v>
       </c>
       <c r="G5">
-        <v>20.1</v>
+        <v>20.12</v>
       </c>
       <c r="H5">
-        <v>0.23</v>
+        <v>10.83</v>
       </c>
       <c r="I5" t="s">
         <v>32</v>
@@ -650,13 +650,13 @@
         <v>100</v>
       </c>
       <c r="F6">
-        <v>0.5</v>
+        <v>37.45</v>
       </c>
       <c r="G6">
-        <v>0.3</v>
+        <v>22.9</v>
       </c>
       <c r="H6">
-        <v>0.13</v>
+        <v>10.11</v>
       </c>
       <c r="I6" t="s">
         <v>33</v>
@@ -673,16 +673,16 @@
         <v>27</v>
       </c>
       <c r="E7">
-        <v>69.52</v>
+        <v>69.54000000000001</v>
       </c>
       <c r="F7">
-        <v>32.3</v>
+        <v>32.29</v>
       </c>
       <c r="G7">
-        <v>12.24</v>
+        <v>12.25</v>
       </c>
       <c r="H7">
-        <v>0.12</v>
+        <v>5.42</v>
       </c>
       <c r="I7" t="s">
         <v>34</v>
@@ -699,16 +699,16 @@
         <v>28</v>
       </c>
       <c r="E8">
-        <v>58.49</v>
+        <v>58.54</v>
       </c>
       <c r="F8">
         <v>33.06</v>
       </c>
       <c r="G8">
-        <v>0.24</v>
+        <v>11.72</v>
       </c>
       <c r="H8">
-        <v>0.09</v>
+        <v>4.41</v>
       </c>
       <c r="I8" t="s">
         <v>35</v>
@@ -725,16 +725,16 @@
         <v>28</v>
       </c>
       <c r="E9">
-        <v>64.48999999999999</v>
+        <v>64.56</v>
       </c>
       <c r="F9">
-        <v>33.56</v>
+        <v>33.66</v>
       </c>
       <c r="G9">
-        <v>0.23</v>
+        <v>11.53</v>
       </c>
       <c r="H9">
-        <v>0.08</v>
+        <v>4.2</v>
       </c>
       <c r="I9" t="s">
         <v>36</v>
@@ -751,16 +751,16 @@
         <v>28</v>
       </c>
       <c r="E10">
-        <v>41.51</v>
+        <v>41.47</v>
       </c>
       <c r="F10">
-        <v>20.07</v>
+        <v>20.01</v>
       </c>
       <c r="G10">
-        <v>0.13</v>
+        <v>5.66</v>
       </c>
       <c r="H10">
-        <v>0.04</v>
+        <v>1.72</v>
       </c>
       <c r="I10" t="s">
         <v>37</v>
@@ -777,16 +777,16 @@
         <v>28</v>
       </c>
       <c r="E11">
-        <v>35.51</v>
+        <v>35.44</v>
       </c>
       <c r="F11">
-        <v>13.31</v>
+        <v>13.27</v>
       </c>
       <c r="G11">
-        <v>0.09</v>
+        <v>2.96</v>
       </c>
       <c r="H11">
-        <v>0.02</v>
+        <v>0.71</v>
       </c>
       <c r="I11" t="s">
         <v>38</v>
@@ -803,16 +803,16 @@
         <v>26</v>
       </c>
       <c r="E12">
-        <v>25.88</v>
+        <v>25.87</v>
       </c>
       <c r="F12">
-        <v>6.34</v>
+        <v>6.32</v>
       </c>
       <c r="G12">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="H12">
-        <v>0.02</v>
+        <v>0.64</v>
       </c>
       <c r="I12" t="s">
         <v>39</v>
@@ -829,16 +829,16 @@
         <v>27</v>
       </c>
       <c r="E13">
-        <v>30.48</v>
+        <v>30.46</v>
       </c>
       <c r="F13">
-        <v>8.380000000000001</v>
+        <v>8.42</v>
       </c>
       <c r="G13">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="H13">
-        <v>0.01</v>
+        <v>0.49</v>
       </c>
       <c r="I13" t="s">
         <v>40</v>
@@ -855,16 +855,16 @@
         <v>26</v>
       </c>
       <c r="E14">
-        <v>17.38</v>
+        <v>17.27</v>
       </c>
       <c r="F14">
-        <v>5.27</v>
+        <v>5.28</v>
       </c>
       <c r="G14">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="H14">
-        <v>0.01</v>
+        <v>0.47</v>
       </c>
       <c r="I14" t="s">
         <v>41</v>

--- a/sim-output/dallas-2026_results.xlsx
+++ b/sim-output/dallas-2026_results.xlsx
@@ -76,12 +76,12 @@
     <t>Miomir Kecmanovic</t>
   </si>
   <si>
+    <t>Adrian Mannarino</t>
+  </si>
+  <si>
     <t>Aleksandar Kovacevic</t>
   </si>
   <si>
-    <t>Adrian Mannarino</t>
-  </si>
-  <si>
     <t>Brandon Nakashima</t>
   </si>
   <si>
@@ -103,43 +103,43 @@
     <t>Q2</t>
   </si>
   <si>
-    <t>+292</t>
-  </si>
-  <si>
-    <t>+320</t>
-  </si>
-  <si>
-    <t>+758</t>
-  </si>
-  <si>
-    <t>+823</t>
-  </si>
-  <si>
-    <t>+890</t>
-  </si>
-  <si>
-    <t>+1744</t>
-  </si>
-  <si>
-    <t>+2165</t>
-  </si>
-  <si>
-    <t>+2282</t>
-  </si>
-  <si>
-    <t>+5730</t>
-  </si>
-  <si>
-    <t>+13898</t>
-  </si>
-  <si>
-    <t>+15608</t>
-  </si>
-  <si>
-    <t>+20430</t>
-  </si>
-  <si>
-    <t>+21006</t>
+    <t>+296</t>
+  </si>
+  <si>
+    <t>+311</t>
+  </si>
+  <si>
+    <t>+785</t>
+  </si>
+  <si>
+    <t>+802</t>
+  </si>
+  <si>
+    <t>+903</t>
+  </si>
+  <si>
+    <t>+1661</t>
+  </si>
+  <si>
+    <t>+2197</t>
+  </si>
+  <si>
+    <t>+2320</t>
+  </si>
+  <si>
+    <t>+5757</t>
+  </si>
+  <si>
+    <t>+13878</t>
+  </si>
+  <si>
+    <t>+16189</t>
+  </si>
+  <si>
+    <t>+22231</t>
+  </si>
+  <si>
+    <t>+22915</t>
   </si>
   <si>
     <t>N/A</t>
@@ -549,10 +549,10 @@
         <v>62.55</v>
       </c>
       <c r="G2">
-        <v>45.22</v>
+        <v>45.21</v>
       </c>
       <c r="H2">
-        <v>25.53</v>
+        <v>25.25</v>
       </c>
       <c r="I2" t="s">
         <v>29</v>
@@ -569,16 +569,16 @@
         <v>26</v>
       </c>
       <c r="E3">
-        <v>82.73</v>
+        <v>83.05</v>
       </c>
       <c r="F3">
-        <v>54.45</v>
+        <v>54.76</v>
       </c>
       <c r="G3">
-        <v>37.49</v>
+        <v>37.9</v>
       </c>
       <c r="H3">
-        <v>23.81</v>
+        <v>24.32</v>
       </c>
       <c r="I3" t="s">
         <v>30</v>
@@ -598,13 +598,13 @@
         <v>100</v>
       </c>
       <c r="F4">
-        <v>59.29</v>
+        <v>58.75</v>
       </c>
       <c r="G4">
-        <v>24.47</v>
+        <v>23.77</v>
       </c>
       <c r="H4">
-        <v>11.66</v>
+        <v>11.3</v>
       </c>
       <c r="I4" t="s">
         <v>31</v>
@@ -621,16 +621,16 @@
         <v>26</v>
       </c>
       <c r="E5">
-        <v>74.13</v>
+        <v>74.64</v>
       </c>
       <c r="F5">
-        <v>33.95</v>
+        <v>34.1</v>
       </c>
       <c r="G5">
-        <v>20.12</v>
+        <v>20.33</v>
       </c>
       <c r="H5">
-        <v>10.83</v>
+        <v>11.09</v>
       </c>
       <c r="I5" t="s">
         <v>32</v>
@@ -653,10 +653,10 @@
         <v>37.45</v>
       </c>
       <c r="G6">
-        <v>22.9</v>
+        <v>22.88</v>
       </c>
       <c r="H6">
-        <v>10.11</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="I6" t="s">
         <v>33</v>
@@ -673,16 +673,16 @@
         <v>27</v>
       </c>
       <c r="E7">
-        <v>69.54000000000001</v>
+        <v>70.73</v>
       </c>
       <c r="F7">
-        <v>32.29</v>
+        <v>33.36</v>
       </c>
       <c r="G7">
-        <v>12.25</v>
+        <v>12.66</v>
       </c>
       <c r="H7">
-        <v>5.42</v>
+        <v>5.68</v>
       </c>
       <c r="I7" t="s">
         <v>34</v>
@@ -699,16 +699,16 @@
         <v>28</v>
       </c>
       <c r="E8">
-        <v>58.54</v>
+        <v>58.46</v>
       </c>
       <c r="F8">
-        <v>33.06</v>
+        <v>33.04</v>
       </c>
       <c r="G8">
-        <v>11.72</v>
+        <v>11.71</v>
       </c>
       <c r="H8">
-        <v>4.41</v>
+        <v>4.35</v>
       </c>
       <c r="I8" t="s">
         <v>35</v>
@@ -725,16 +725,16 @@
         <v>28</v>
       </c>
       <c r="E9">
-        <v>64.56</v>
+        <v>64.47</v>
       </c>
       <c r="F9">
-        <v>33.66</v>
+        <v>33.59</v>
       </c>
       <c r="G9">
-        <v>11.53</v>
+        <v>11.52</v>
       </c>
       <c r="H9">
-        <v>4.2</v>
+        <v>4.13</v>
       </c>
       <c r="I9" t="s">
         <v>36</v>
@@ -751,16 +751,16 @@
         <v>28</v>
       </c>
       <c r="E10">
-        <v>41.47</v>
+        <v>41.54</v>
       </c>
       <c r="F10">
-        <v>20.01</v>
+        <v>20.04</v>
       </c>
       <c r="G10">
-        <v>5.66</v>
+        <v>5.69</v>
       </c>
       <c r="H10">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="I10" t="s">
         <v>37</v>
@@ -777,16 +777,16 @@
         <v>28</v>
       </c>
       <c r="E11">
-        <v>35.44</v>
+        <v>35.53</v>
       </c>
       <c r="F11">
-        <v>13.27</v>
+        <v>13.33</v>
       </c>
       <c r="G11">
-        <v>2.96</v>
+        <v>2.99</v>
       </c>
       <c r="H11">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="I11" t="s">
         <v>38</v>
@@ -803,16 +803,16 @@
         <v>26</v>
       </c>
       <c r="E12">
-        <v>25.87</v>
+        <v>25.36</v>
       </c>
       <c r="F12">
-        <v>6.32</v>
+        <v>6.06</v>
       </c>
       <c r="G12">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="H12">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="I12" t="s">
         <v>39</v>
@@ -823,22 +823,22 @@
         <v>20</v>
       </c>
       <c r="C13">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E13">
-        <v>30.46</v>
+        <v>16.95</v>
       </c>
       <c r="F13">
-        <v>8.42</v>
+        <v>5.07</v>
       </c>
       <c r="G13">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="H13">
-        <v>0.49</v>
+        <v>0.45</v>
       </c>
       <c r="I13" t="s">
         <v>40</v>
@@ -849,22 +849,22 @@
         <v>21</v>
       </c>
       <c r="C14">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D14" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E14">
-        <v>17.27</v>
+        <v>29.27</v>
       </c>
       <c r="F14">
-        <v>5.28</v>
+        <v>7.89</v>
       </c>
       <c r="G14">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="H14">
-        <v>0.47</v>
+        <v>0.43</v>
       </c>
       <c r="I14" t="s">
         <v>41</v>

--- a/sim-output/dallas-2026_results.xlsx
+++ b/sim-output/dallas-2026_results.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="40">
   <si>
     <t>Player</t>
   </si>
@@ -49,45 +49,45 @@
     <t>Ben Shelton</t>
   </si>
   <si>
+    <t>Tommy Paul</t>
+  </si>
+  <si>
+    <t>Sebastian Korda</t>
+  </si>
+  <si>
     <t>Alejandro Davidovich Fokina</t>
   </si>
   <si>
-    <t>Tommy Paul</t>
-  </si>
-  <si>
-    <t>Sebastian Korda</t>
-  </si>
-  <si>
     <t>Denis Shapovalov</t>
   </si>
   <si>
     <t>Marin Cilic</t>
   </si>
   <si>
+    <t>Jack Pinnington Jones</t>
+  </si>
+  <si>
+    <t>Miomir Kecmanovic</t>
+  </si>
+  <si>
+    <t>Adrian Mannarino</t>
+  </si>
+  <si>
+    <t>Brandon Nakashima</t>
+  </si>
+  <si>
+    <t>Frances Tiafoe</t>
+  </si>
+  <si>
     <t>Eliot Spizzirri</t>
   </si>
   <si>
     <t>Ethan Quinn</t>
   </si>
   <si>
-    <t>Qualifier1</t>
-  </si>
-  <si>
-    <t>Miomir Kecmanovic</t>
-  </si>
-  <si>
-    <t>Adrian Mannarino</t>
-  </si>
-  <si>
     <t>Aleksandar Kovacevic</t>
   </si>
   <si>
-    <t>Brandon Nakashima</t>
-  </si>
-  <si>
-    <t>Frances Tiafoe</t>
-  </si>
-  <si>
     <t>Alex Michelsen</t>
   </si>
   <si>
@@ -103,43 +103,34 @@
     <t>Q2</t>
   </si>
   <si>
-    <t>+296</t>
-  </si>
-  <si>
-    <t>+311</t>
-  </si>
-  <si>
-    <t>+785</t>
-  </si>
-  <si>
-    <t>+802</t>
-  </si>
-  <si>
-    <t>+903</t>
-  </si>
-  <si>
-    <t>+1661</t>
-  </si>
-  <si>
-    <t>+2197</t>
-  </si>
-  <si>
-    <t>+2320</t>
-  </si>
-  <si>
-    <t>+5757</t>
-  </si>
-  <si>
-    <t>+13878</t>
-  </si>
-  <si>
-    <t>+16189</t>
-  </si>
-  <si>
-    <t>+22231</t>
-  </si>
-  <si>
-    <t>+22915</t>
+    <t>+300</t>
+  </si>
+  <si>
+    <t>+318</t>
+  </si>
+  <si>
+    <t>+831</t>
+  </si>
+  <si>
+    <t>+853</t>
+  </si>
+  <si>
+    <t>+897</t>
+  </si>
+  <si>
+    <t>+1089</t>
+  </si>
+  <si>
+    <t>+1092</t>
+  </si>
+  <si>
+    <t>+4819</t>
+  </si>
+  <si>
+    <t>+17441</t>
+  </si>
+  <si>
+    <t>+23358</t>
   </si>
   <si>
     <t>N/A</t>
@@ -546,13 +537,13 @@
         <v>100</v>
       </c>
       <c r="F2">
-        <v>62.55</v>
+        <v>61.81</v>
       </c>
       <c r="G2">
-        <v>45.21</v>
+        <v>45.01</v>
       </c>
       <c r="H2">
-        <v>25.25</v>
+        <v>25</v>
       </c>
       <c r="I2" t="s">
         <v>29</v>
@@ -572,13 +563,13 @@
         <v>83.05</v>
       </c>
       <c r="F3">
-        <v>54.76</v>
+        <v>54.77</v>
       </c>
       <c r="G3">
-        <v>37.9</v>
+        <v>37.24</v>
       </c>
       <c r="H3">
-        <v>24.32</v>
+        <v>23.92</v>
       </c>
       <c r="I3" t="s">
         <v>30</v>
@@ -589,22 +580,22 @@
         <v>11</v>
       </c>
       <c r="C4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E4">
-        <v>100</v>
+        <v>74.68000000000001</v>
       </c>
       <c r="F4">
-        <v>58.75</v>
+        <v>34.11</v>
       </c>
       <c r="G4">
-        <v>23.77</v>
+        <v>19.8</v>
       </c>
       <c r="H4">
-        <v>11.3</v>
+        <v>10.74</v>
       </c>
       <c r="I4" t="s">
         <v>31</v>
@@ -615,22 +606,22 @@
         <v>12</v>
       </c>
       <c r="C5">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="D5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E5">
-        <v>74.64</v>
+        <v>100</v>
       </c>
       <c r="F5">
-        <v>34.1</v>
+        <v>38.19</v>
       </c>
       <c r="G5">
-        <v>20.33</v>
+        <v>23.89</v>
       </c>
       <c r="H5">
-        <v>11.09</v>
+        <v>10.49</v>
       </c>
       <c r="I5" t="s">
         <v>32</v>
@@ -641,22 +632,22 @@
         <v>13</v>
       </c>
       <c r="C6">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D6" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E6">
         <v>100</v>
       </c>
       <c r="F6">
-        <v>37.45</v>
+        <v>52.1</v>
       </c>
       <c r="G6">
-        <v>22.88</v>
+        <v>21.09</v>
       </c>
       <c r="H6">
-        <v>9.970000000000001</v>
+        <v>10.03</v>
       </c>
       <c r="I6" t="s">
         <v>33</v>
@@ -673,16 +664,16 @@
         <v>27</v>
       </c>
       <c r="E7">
-        <v>70.73</v>
+        <v>100</v>
       </c>
       <c r="F7">
-        <v>33.36</v>
+        <v>47.9</v>
       </c>
       <c r="G7">
-        <v>12.66</v>
+        <v>18.41</v>
       </c>
       <c r="H7">
-        <v>5.68</v>
+        <v>8.41</v>
       </c>
       <c r="I7" t="s">
         <v>34</v>
@@ -699,16 +690,16 @@
         <v>28</v>
       </c>
       <c r="E8">
-        <v>58.46</v>
+        <v>100</v>
       </c>
       <c r="F8">
-        <v>33.04</v>
+        <v>64.52</v>
       </c>
       <c r="G8">
-        <v>11.71</v>
+        <v>22.83</v>
       </c>
       <c r="H8">
-        <v>4.35</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="I8" t="s">
         <v>35</v>
@@ -719,22 +710,22 @@
         <v>16</v>
       </c>
       <c r="C9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D9" t="s">
         <v>28</v>
       </c>
       <c r="E9">
-        <v>64.47</v>
+        <v>100</v>
       </c>
       <c r="F9">
-        <v>33.59</v>
+        <v>35.48</v>
       </c>
       <c r="G9">
-        <v>11.52</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="H9">
-        <v>4.13</v>
+        <v>2.03</v>
       </c>
       <c r="I9" t="s">
         <v>36</v>
@@ -745,22 +736,22 @@
         <v>17</v>
       </c>
       <c r="C10">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D10" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E10">
-        <v>41.54</v>
+        <v>25.32</v>
       </c>
       <c r="F10">
-        <v>20.04</v>
+        <v>6.05</v>
       </c>
       <c r="G10">
-        <v>5.69</v>
+        <v>1.93</v>
       </c>
       <c r="H10">
-        <v>1.71</v>
+        <v>0.57</v>
       </c>
       <c r="I10" t="s">
         <v>37</v>
@@ -771,22 +762,22 @@
         <v>18</v>
       </c>
       <c r="C11">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D11" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E11">
-        <v>35.53</v>
+        <v>16.95</v>
       </c>
       <c r="F11">
-        <v>13.33</v>
+        <v>5.08</v>
       </c>
       <c r="G11">
-        <v>2.99</v>
+        <v>1.52</v>
       </c>
       <c r="H11">
-        <v>0.72</v>
+        <v>0.43</v>
       </c>
       <c r="I11" t="s">
         <v>38</v>
@@ -797,22 +788,22 @@
         <v>19</v>
       </c>
       <c r="C12">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="D12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E12">
-        <v>25.36</v>
+        <v>0</v>
       </c>
       <c r="F12">
-        <v>6.06</v>
+        <v>0</v>
       </c>
       <c r="G12">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="H12">
-        <v>0.61</v>
+        <v>0</v>
       </c>
       <c r="I12" t="s">
         <v>39</v>
@@ -823,25 +814,25 @@
         <v>20</v>
       </c>
       <c r="C13">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="D13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E13">
-        <v>16.95</v>
+        <v>0</v>
       </c>
       <c r="F13">
-        <v>5.07</v>
+        <v>0</v>
       </c>
       <c r="G13">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="H13">
-        <v>0.45</v>
+        <v>0</v>
       </c>
       <c r="I13" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -849,25 +840,25 @@
         <v>21</v>
       </c>
       <c r="C14">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D14" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E14">
-        <v>29.27</v>
+        <v>0</v>
       </c>
       <c r="F14">
-        <v>7.89</v>
+        <v>0</v>
       </c>
       <c r="G14">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="H14">
-        <v>0.43</v>
+        <v>0</v>
       </c>
       <c r="I14" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -875,10 +866,10 @@
         <v>22</v>
       </c>
       <c r="C15">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D15" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -893,7 +884,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -901,10 +892,10 @@
         <v>23</v>
       </c>
       <c r="C16">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D16" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -919,7 +910,7 @@
         <v>0</v>
       </c>
       <c r="I16" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -945,7 +936,7 @@
         <v>0</v>
       </c>
       <c r="I17" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/sim-output/dallas-2026_results.xlsx
+++ b/sim-output/dallas-2026_results.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>Player</t>
   </si>
@@ -28,9 +28,6 @@
     <t>Quarter</t>
   </si>
   <si>
-    <t>SF</t>
-  </si>
-  <si>
     <t>F</t>
   </si>
   <si>
@@ -46,58 +43,34 @@
     <t>Taylor Fritz</t>
   </si>
   <si>
-    <t>Sebastian Korda</t>
+    <t>Denis Shapovalov</t>
   </si>
   <si>
     <t>Marin Cilic</t>
   </si>
   <si>
-    <t>Denis Shapovalov</t>
-  </si>
-  <si>
-    <t>Alejandro Davidovich Fokina</t>
-  </si>
-  <si>
-    <t>Miomir Kecmanovic</t>
-  </si>
-  <si>
-    <t>Jack Pinnington Jones</t>
-  </si>
-  <si>
     <t>Q4</t>
   </si>
   <si>
     <t>Q1</t>
   </si>
   <si>
+    <t>Q3</t>
+  </si>
+  <si>
     <t>Q2</t>
   </si>
   <si>
-    <t>Q3</t>
-  </si>
-  <si>
-    <t>+191</t>
-  </si>
-  <si>
-    <t>+331</t>
-  </si>
-  <si>
-    <t>+838</t>
-  </si>
-  <si>
-    <t>+873</t>
-  </si>
-  <si>
-    <t>+877</t>
-  </si>
-  <si>
-    <t>+1063</t>
-  </si>
-  <si>
-    <t>+5776</t>
-  </si>
-  <si>
-    <t>+9813</t>
+    <t>+170</t>
+  </si>
+  <si>
+    <t>+228</t>
+  </si>
+  <si>
+    <t>+473</t>
+  </si>
+  <si>
+    <t>+562</t>
   </si>
 </sst>
 </file>
@@ -455,10 +428,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -480,192 +453,85 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" t="s">
         <v>7</v>
       </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2">
+        <v>62.58</v>
+      </c>
+      <c r="F2">
+        <v>36.99</v>
+      </c>
+      <c r="G2" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="2" spans="1:8">
-      <c r="A2" t="s">
+    <row r="3" spans="1:7">
+      <c r="A3" t="s">
         <v>8</v>
-      </c>
-      <c r="C2">
-        <v>8</v>
-      </c>
-      <c r="D2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E2">
-        <v>81.37</v>
-      </c>
-      <c r="F2">
-        <v>54.28</v>
-      </c>
-      <c r="G2">
-        <v>34.35</v>
-      </c>
-      <c r="H2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3" t="s">
-        <v>9</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
       <c r="D3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3">
+        <v>61.18</v>
+      </c>
+      <c r="F3">
+        <v>30.45</v>
+      </c>
+      <c r="G3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4">
+        <v>3</v>
+      </c>
+      <c r="D4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4">
+        <v>37.42</v>
+      </c>
+      <c r="F4">
+        <v>17.45</v>
+      </c>
+      <c r="G4" t="s">
         <v>17</v>
       </c>
-      <c r="E3">
-        <v>60.5</v>
-      </c>
-      <c r="F3">
-        <v>43.05</v>
-      </c>
-      <c r="G3">
-        <v>23.18</v>
-      </c>
-      <c r="H3" t="s">
-        <v>21</v>
-      </c>
     </row>
-    <row r="4" spans="1:8">
-      <c r="A4" t="s">
+    <row r="5" spans="1:7">
+      <c r="A5" t="s">
         <v>10</v>
       </c>
-      <c r="C4">
+      <c r="C5">
         <v>2</v>
       </c>
-      <c r="D4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E4">
-        <v>39.5</v>
-      </c>
-      <c r="F4">
-        <v>24.51</v>
-      </c>
-      <c r="G4">
-        <v>10.66</v>
-      </c>
-      <c r="H4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5">
-        <v>4</v>
-      </c>
       <c r="D5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5">
+        <v>38.82</v>
+      </c>
+      <c r="F5">
+        <v>15.1</v>
+      </c>
+      <c r="G5" t="s">
         <v>18</v>
-      </c>
-      <c r="E5">
-        <v>72.48999999999999</v>
-      </c>
-      <c r="F5">
-        <v>27.26</v>
-      </c>
-      <c r="G5">
-        <v>10.28</v>
-      </c>
-      <c r="H5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6">
-        <v>5</v>
-      </c>
-      <c r="D6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E6">
-        <v>52.09</v>
-      </c>
-      <c r="F6">
-        <v>21.25</v>
-      </c>
-      <c r="G6">
-        <v>10.23</v>
-      </c>
-      <c r="H6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7">
-        <v>6</v>
-      </c>
-      <c r="D7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E7">
-        <v>47.91</v>
-      </c>
-      <c r="F7">
-        <v>18.64</v>
-      </c>
-      <c r="G7">
-        <v>8.59</v>
-      </c>
-      <c r="H7" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" t="s">
-        <v>14</v>
-      </c>
-      <c r="C8">
-        <v>7</v>
-      </c>
-      <c r="D8" t="s">
-        <v>16</v>
-      </c>
-      <c r="E8">
-        <v>18.63</v>
-      </c>
-      <c r="F8">
-        <v>5.84</v>
-      </c>
-      <c r="G8">
-        <v>1.7</v>
-      </c>
-      <c r="H8" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9" t="s">
-        <v>15</v>
-      </c>
-      <c r="C9">
-        <v>3</v>
-      </c>
-      <c r="D9" t="s">
-        <v>18</v>
-      </c>
-      <c r="E9">
-        <v>27.51</v>
-      </c>
-      <c r="F9">
-        <v>5.18</v>
-      </c>
-      <c r="G9">
-        <v>1.01</v>
-      </c>
-      <c r="H9" t="s">
-        <v>27</v>
       </c>
     </row>
   </sheetData>
